--- a/utils/monday_sprint_sprint_2024-31.xlsx
+++ b/utils/monday_sprint_sprint_2024-31.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="165">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>24304</t>
+    <t>5990322959</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>02/02/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>13/03/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>24491</t>
+    <t>6034619226</t>
   </si>
   <si>
     <t>Alteração relatórios ensaio mecânico</t>
@@ -111,10 +111,13 @@
     <t>09/02/2024</t>
   </si>
   <si>
+    <t>17/03/2024</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>23325</t>
+    <t>6144886096</t>
   </si>
   <si>
     <t>Reduzir tempo de impressão</t>
@@ -126,10 +129,13 @@
     <t>27/02/2024</t>
   </si>
   <si>
+    <t>18/03/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>24613</t>
+    <t>6175390833</t>
   </si>
   <si>
     <t>OTF 157712 | Komatsu Peoria</t>
@@ -162,7 +168,7 @@
     <t>6190307486</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>6004011273</t>
   </si>
   <si>
     <t>Tratamento de erros</t>
@@ -171,34 +177,46 @@
     <t>05/02/2024</t>
   </si>
   <si>
-    <t>24677</t>
+    <t>6175456446</t>
   </si>
   <si>
     <t>Fluxo de caixa</t>
   </si>
   <si>
+    <t>14/03/2024</t>
+  </si>
+  <si>
+    <t>6185188167</t>
+  </si>
+  <si>
     <t>Projeto</t>
   </si>
   <si>
     <t>Interface de envio  das informações para eFact pelo usuário</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>6185322620</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint 5</t>
   </si>
   <si>
-    <t>21601</t>
+    <t>15/03/2024</t>
+  </si>
+  <si>
+    <t>6185396435</t>
   </si>
   <si>
     <t>GERAÇÃO DE ROMANEIO - EXPEDIÇÃO</t>
   </si>
   <si>
+    <t>6186538844</t>
+  </si>
+  <si>
     <t>Tratamento de erros dados mestres</t>
   </si>
   <si>
-    <t>24229</t>
+    <t>5912558210</t>
   </si>
   <si>
     <t>Unificar seq SEM pedidos e COM pedidos</t>
@@ -210,13 +228,13 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>24260</t>
+    <t>5990596602</t>
   </si>
   <si>
     <t>Movimentação retroativa</t>
   </si>
   <si>
-    <t>24349</t>
+    <t>6026466092</t>
   </si>
   <si>
     <t>Ajuste de dupla checagem de composição química - Analise critica</t>
@@ -225,28 +243,31 @@
     <t>08/02/2024</t>
   </si>
   <si>
+    <t>6026469053</t>
+  </si>
+  <si>
     <t>Ajuste de dupla checagem de composição química - CPP</t>
   </si>
   <si>
-    <t>24468</t>
+    <t>6034688098</t>
   </si>
   <si>
     <t>BUG PRE-EMBARQUE - ID em branco</t>
   </si>
   <si>
-    <t>24461</t>
+    <t>6034706655</t>
   </si>
   <si>
     <t>Regras de automatização CST</t>
   </si>
   <si>
-    <t>24303</t>
+    <t>6034785021</t>
   </si>
   <si>
     <t>Indicadores 5S</t>
   </si>
   <si>
-    <t>24599</t>
+    <t>6080345692</t>
   </si>
   <si>
     <t>Melhorias - Posto de Cópia Eletrônico</t>
@@ -258,121 +279,136 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>24553</t>
+    <t>6080591919</t>
   </si>
   <si>
     <t>Alterar transportadora &amp; Nome do Motorista</t>
   </si>
   <si>
-    <t>24327</t>
+    <t>6144876172</t>
   </si>
   <si>
     <t>ALTERAR IMPRESSORA ROMANEIO</t>
   </si>
   <si>
-    <t>24886</t>
+    <t>6174749827</t>
   </si>
   <si>
     <t>Inclusão da informação família nos relatórios e Status no FUP</t>
   </si>
   <si>
-    <t>24876</t>
+    <t>07/03/2024</t>
+  </si>
+  <si>
+    <t>6175156557</t>
   </si>
   <si>
     <t>Inserir pergunta MPO</t>
   </si>
   <si>
-    <t>24863</t>
+    <t>6175174355</t>
   </si>
   <si>
     <t>Sistema de corridas</t>
   </si>
   <si>
-    <t>24845</t>
+    <t>6175209344</t>
   </si>
   <si>
     <t>Alteração Relatório de Notas despachadas</t>
   </si>
   <si>
-    <t>24809</t>
+    <t>6175251290</t>
   </si>
   <si>
     <t>Melhoria consulta de corridas</t>
   </si>
   <si>
-    <t>24803</t>
+    <t>05/03/2024</t>
+  </si>
+  <si>
+    <t>6175273114</t>
   </si>
   <si>
     <t>Requisição Materiais Estoque Altona.</t>
   </si>
   <si>
-    <t>24796</t>
+    <t>6175308109</t>
   </si>
   <si>
     <t>Melhoria no relatório de pendencias</t>
   </si>
   <si>
-    <t>24763</t>
+    <t>06/03/2024</t>
+  </si>
+  <si>
+    <t>6175337961</t>
   </si>
   <si>
     <t>3D de conjunto</t>
   </si>
   <si>
-    <t>24761</t>
+    <t>6175349383</t>
   </si>
   <si>
     <t>ALTERAÇÃO DE CHECKLIST 516</t>
   </si>
   <si>
-    <t>24702</t>
+    <t>6175398102</t>
   </si>
   <si>
     <t>Pontos de melhorias no sistema</t>
   </si>
   <si>
-    <t>24665</t>
+    <t>6175469805</t>
   </si>
   <si>
     <t>Melhoria Relatório Apontamentos Moldagem USE/ULE/MACHARIA</t>
   </si>
   <si>
-    <t>24658</t>
+    <t>6175514336</t>
   </si>
   <si>
     <t>Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>24812</t>
+    <t>6175656631</t>
   </si>
   <si>
     <t>liberar a movimentação em lote da aciaria e moldagem</t>
   </si>
   <si>
-    <t>24899</t>
+    <t>6176813876</t>
   </si>
   <si>
     <t>Alteração nos limites mínimos e máximos de temperaturas de tratamento térmico na Análise</t>
   </si>
   <si>
+    <t>6185280286</t>
+  </si>
+  <si>
+    <t>6185295831</t>
+  </si>
+  <si>
     <t>Ajuste de dupla checagem de composição química - Homologação</t>
   </si>
   <si>
-    <t>24071</t>
+    <t>10/03/2024</t>
+  </si>
+  <si>
+    <t>6198003021</t>
   </si>
   <si>
     <t>Inserir coluna "Corrida" na planilha MPS</t>
   </si>
   <si>
-    <t>05/03/2024</t>
-  </si>
-  <si>
-    <t>24595</t>
+    <t>6080357940</t>
   </si>
   <si>
     <t>Caracteres e-mail desmoldagem</t>
   </si>
   <si>
-    <t>23628</t>
+    <t>6090738889</t>
   </si>
   <si>
     <t>Homologação Sistema Honda</t>
@@ -387,7 +423,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-31</t>
+    <t>Jan/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1032,7 +1068,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1041,7 +1077,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1049,7 +1085,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1061,13 +1097,13 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
@@ -1076,10 +1112,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1088,7 +1124,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1096,7 +1132,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1108,10 +1144,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1123,10 +1159,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1138,30 +1174,30 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1170,10 +1206,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1185,31 +1221,31 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
       </c>
@@ -1217,10 +1253,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1232,42 +1268,42 @@
         <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1279,12 +1315,12 @@
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1296,10 +1332,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1311,7 +1347,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
@@ -1331,7 +1367,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1343,10 +1379,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1358,10 +1394,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1373,30 +1409,30 @@
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1405,7 +1441,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>24</v>
@@ -1420,27 +1456,27 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1452,10 +1488,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1467,30 +1503,30 @@
         <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -1499,10 +1535,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1514,27 +1550,27 @@
         <v>27</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1546,7 +1582,7 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -1561,12 +1597,12 @@
         <v>27</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1578,10 +1614,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1593,10 +1629,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1605,15 +1641,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1625,10 +1661,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1643,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1660,7 +1696,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1672,10 +1708,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1687,10 +1723,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1699,7 +1735,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1707,7 +1743,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1719,10 +1755,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1734,10 +1770,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1746,7 +1782,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1754,7 +1790,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1766,10 +1802,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1784,7 +1820,7 @@
         <v>31</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1793,7 +1829,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1801,7 +1837,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1813,10 +1849,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1831,7 +1867,7 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1840,7 +1876,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1848,7 +1884,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1860,10 +1896,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1878,7 +1914,7 @@
         <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1887,7 +1923,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1895,7 +1931,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1907,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1922,10 +1958,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1934,7 +1970,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -1942,7 +1978,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1954,10 +1990,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1969,10 +2005,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1981,7 +2017,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -1989,7 +2025,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2001,13 +2037,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -2016,10 +2052,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2028,7 +2064,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2036,7 +2072,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2048,10 +2084,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2063,10 +2099,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2078,12 +2114,12 @@
         <v>27</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2095,10 +2131,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2110,10 +2146,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2125,12 +2161,12 @@
         <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2142,10 +2178,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2157,10 +2193,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2172,12 +2208,12 @@
         <v>27</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2189,10 +2225,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2204,10 +2240,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2219,12 +2255,12 @@
         <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2236,10 +2272,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2251,10 +2287,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2266,12 +2302,12 @@
         <v>27</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2283,10 +2319,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2298,7 +2334,7 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -2313,12 +2349,12 @@
         <v>27</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2330,10 +2366,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2345,10 +2381,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2360,12 +2396,12 @@
         <v>27</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2377,10 +2413,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2392,10 +2428,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2407,12 +2443,12 @@
         <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2424,10 +2460,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2439,10 +2475,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2454,42 +2490,42 @@
         <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2501,12 +2537,12 @@
         <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2518,10 +2554,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2533,10 +2569,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2548,12 +2584,12 @@
         <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2565,10 +2601,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2580,10 +2616,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2595,12 +2631,12 @@
         <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2612,10 +2648,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2627,10 +2663,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2642,12 +2678,12 @@
         <v>27</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2659,10 +2695,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2674,10 +2710,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2689,12 +2725,12 @@
         <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2721,10 +2757,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2736,12 +2772,12 @@
         <v>27</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2753,10 +2789,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2768,10 +2804,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2783,12 +2819,12 @@
         <v>27</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2800,10 +2836,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2815,10 +2851,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2830,12 +2866,12 @@
         <v>27</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2847,10 +2883,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2862,10 +2898,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2874,7 +2910,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2882,22 +2918,22 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2909,10 +2945,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2921,7 +2957,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2940,23 +2976,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2964,16 +3000,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2984,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2992,7 +3028,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3005,7 +3041,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3013,7 +3049,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3044,12 +3080,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B2">
         <v>42</v>
@@ -3063,7 +3099,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3073,25 +3109,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3108,13 +3144,13 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3129,18 +3165,18 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -3152,21 +3188,21 @@
         <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3178,53 +3214,47 @@
         <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Q12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3232,7 +3262,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3240,7 +3270,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3248,7 +3278,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3256,10 +3286,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3267,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3275,142 +3305,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2">
         <v>42</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
